--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488181_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488181_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1879</v>
+        <v>5.2699</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0687</v>
+        <v>7.0029</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8808</v>
+        <v>-1.733</v>
       </c>
       <c r="G2" t="n">
         <v>2.4871</v>
@@ -610,13 +610,13 @@
         <v>2.2234</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5122</v>
+        <v>1.5942</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2794</v>
+        <v>1.2137</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2328</v>
+        <v>0.3805</v>
       </c>
       <c r="V2" t="n">
         <v>0.8179999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4095</v>
+        <v>-0.7448</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3637</v>
+        <v>-1.9945</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9543</v>
+        <v>1.2497</v>
       </c>
       <c r="G4" t="n">
         <v>-0.628</v>
@@ -766,13 +766,13 @@
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0861</v>
+        <v>0.7508</v>
       </c>
       <c r="T4" t="n">
-        <v>1.302</v>
+        <v>0.6712</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2159</v>
+        <v>0.0796</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1264</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8771</v>
+        <v>-1.6611</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2055</v>
+        <v>-0.891</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6716</v>
+        <v>-0.7701</v>
       </c>
       <c r="G5" t="n">
         <v>-2.559</v>
@@ -844,13 +844,13 @@
         <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3495</v>
+        <v>0.5655</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1291</v>
+        <v>0.4436</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2203</v>
+        <v>0.1219</v>
       </c>
       <c r="V5" t="n">
         <v>1.2589</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8303</v>
+        <v>-1.7756</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.0916</v>
+        <v>-3.0369</v>
       </c>
       <c r="F6" t="n">
         <v>1.2613</v>
@@ -922,10 +922,10 @@
         <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4253</v>
+        <v>0.48</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2151</v>
+        <v>0.2699</v>
       </c>
       <c r="U6" t="n">
         <v>0.2101</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.6943</v>
+        <v>-3.4533</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.265</v>
+        <v>-3.49</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4293</v>
+        <v>0.0367</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1441</v>
+        <v>-2.8459</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4635</v>
+        <v>-1.651</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3195</v>
+        <v>-1.1949</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7815</v>
+        <v>-0.8683</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2198</v>
+        <v>-0.4643</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0013</v>
+        <v>-0.404</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9255</v>
+        <v>-1.9775</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2437</v>
+        <v>-1.1867</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6818</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0382</v>
+        <v>0.1853</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.7057</v>
+        <v>-2.7793</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6676</v>
+        <v>2.9646</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5121</v>
+        <v>0.277</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3407</v>
+        <v>0.1576</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1714</v>
+        <v>0.1194</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0697</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0697</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7356</v>
+        <v>-3.4943</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.778</v>
+        <v>-1.1058</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0423</v>
+        <v>-2.3885</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5889</v>
+        <v>-4.5494</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4078</v>
+        <v>-1.5848</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1811</v>
+        <v>-2.9646</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4785</v>
+        <v>-0.4137</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.52</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0415</v>
+        <v>0.115</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1104</v>
+        <v>-4.1357</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8878</v>
+        <v>-1.0561</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2226</v>
+        <v>-3.0796</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.4087</v>
+        <v>0.9264</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>1.297</v>
+        <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3885</v>
+        <v>0.1287</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2226</v>
+        <v>0.2344</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6111</v>
+        <v>-0.1057</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1264</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7448</v>
+        <v>-3.597</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3563</v>
+        <v>-3.0691</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3885</v>
+        <v>-0.5278</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.5494</v>
+        <v>-1.1441</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5848</v>
+        <v>-1.4635</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9646</v>
+        <v>0.3195</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4137</v>
+        <v>0.7815</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-1.2198</v>
       </c>
       <c r="L9" t="n">
-        <v>0.115</v>
+        <v>2.0013</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.1357</v>
+        <v>-1.9255</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0561</v>
+        <v>-0.2437</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.0796</v>
+        <v>-1.6818</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9264</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1219</v>
+        <v>-0.4147</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0161</v>
+        <v>-0.1449</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1057</v>
+        <v>-0.2699</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5371</v>
+        <v>-3.8483</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4261</v>
+        <v>-3.5706</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1111</v>
+        <v>-0.2777</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8459</v>
+        <v>-1.5889</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.651</v>
+        <v>-1.4078</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1949</v>
+        <v>-0.1811</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8683</v>
+        <v>-0.4785</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4643</v>
+        <v>-0.52</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.404</v>
+        <v>0.0415</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9775</v>
+        <v>-1.1104</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1867</v>
+        <v>-0.8878</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.2226</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1853</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7793</v>
+        <v>-3.7057</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9646</v>
+        <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8068</v>
+        <v>0.2758</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7784</v>
+        <v>-0.0152</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0284</v>
+        <v>0.291</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0697</v>
+        <v>-0.1264</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0697</v>
+        <v>-0.7553</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8398</v>
+        <v>-4.0744</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2404</v>
+        <v>-1.5982</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5993</v>
+        <v>-2.4762</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7788</v>
@@ -1312,13 +1312,13 @@
         <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6168</v>
+        <v>0.1486</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4377</v>
+        <v>0.2046</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1791</v>
+        <v>-0.056</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2589</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>A. VICENTE FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1624</v>
+        <v>-5.6816</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.292</v>
+        <v>-2.4477</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8704</v>
+        <v>-3.2339</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4203</v>
+        <v>-2.627</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1055</v>
+        <v>-1.6945</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3148</v>
+        <v>-0.9325</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4713</v>
+        <v>-0.472</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5542</v>
+        <v>-0.5455</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0829</v>
+        <v>0.0735</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.949</v>
+        <v>-2.155</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5513</v>
+        <v>-1.149</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3977</v>
+        <v>-1.006</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2197</v>
+        <v>-0.1663</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0321</v>
+        <v>-0.1228</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1875</v>
+        <v>-0.0435</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.7766</v>
+        <v>-2.5177</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.7766</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. VICENTE FERNANDEZ</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.9015</v>
+        <v>-5.7019</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7414</v>
+        <v>-1.6837</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1601</v>
+        <v>-4.0182</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.627</v>
+        <v>-2.4203</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6945</v>
+        <v>-1.1055</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9325</v>
+        <v>-1.3148</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.472</v>
+        <v>-0.4713</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5455</v>
+        <v>-0.5542</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0735</v>
+        <v>0.0829</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.155</v>
+        <v>-1.949</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.149</v>
+        <v>-0.5513</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.006</v>
+        <v>-1.3977</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3706</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3862</v>
+        <v>0.6802</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4166</v>
+        <v>0.6404</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0303</v>
+        <v>0.0398</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.5177</v>
+        <v>-3.7766</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.5177</v>
+        <v>-3.7766</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.5167</v>
+        <v>-8.751799999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.5942</v>
+        <v>-3.854</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.9224</v>
+        <v>-4.8978</v>
       </c>
       <c r="G14" t="n">
         <v>-5.8903</v>
@@ -1546,13 +1546,13 @@
         <v>1.1117</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6824</v>
+        <v>0.0824</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5807</v>
+        <v>0.1595</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1017</v>
+        <v>-0.0771</v>
       </c>
       <c r="V14" t="n">
         <v>-2.2027</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-34.9067</v>
+        <v>-34.3597</v>
       </c>
       <c r="E15" t="n">
-        <v>-17.131</v>
+        <v>-16.5841</v>
       </c>
       <c r="F15" t="n">
-        <v>-17.7756</v>
+        <v>-17.7755</v>
       </c>
       <c r="G15" t="n">
         <v>-23.1492</v>
@@ -1597,13 +1597,13 @@
         <v>-9.715</v>
       </c>
       <c r="J15" t="n">
-        <v>1.239800000000001</v>
+        <v>1.239799999999999</v>
       </c>
       <c r="K15" t="n">
         <v>-3.482200000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>4.7221</v>
+        <v>4.722100000000001</v>
       </c>
       <c r="M15" t="n">
         <v>-24.3889</v>
@@ -1624,16 +1624,16 @@
         <v>19.4551</v>
       </c>
       <c r="S15" t="n">
-        <v>3.855100000000001</v>
+        <v>4.4022</v>
       </c>
       <c r="T15" t="n">
-        <v>3.164899999999999</v>
+        <v>3.712</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6899</v>
+        <v>0.6900999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-9.1274</v>
+        <v>-9.127400000000002</v>
       </c>
       <c r="W15" t="n">
         <v>4.4044</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>15.0103</v>
+        <v>15.8109</v>
       </c>
       <c r="E16" t="n">
-        <v>12.7316</v>
+        <v>13.1233</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2787</v>
+        <v>2.6876</v>
       </c>
       <c r="G16" t="n">
         <v>11.1605</v>
@@ -1702,13 +1702,13 @@
         <v>3.3352</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0767</v>
+        <v>-0.2761</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4166</v>
+        <v>-0.0249</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6601</v>
+        <v>-0.2512</v>
       </c>
       <c r="V16" t="n">
         <v>2.5177</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2999</v>
+        <v>3.631</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6395</v>
+        <v>0.6602</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6604</v>
+        <v>2.9708</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2566</v>
@@ -1780,13 +1780,13 @@
         <v>2.7793</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4268</v>
+        <v>0.7579</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4873</v>
+        <v>0.508</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0605</v>
+        <v>0.2499</v>
       </c>
       <c r="V17" t="n">
         <v>2.2033</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3246</v>
+        <v>3.5185</v>
       </c>
       <c r="E18" t="n">
-        <v>2.023</v>
+        <v>1.2556</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3016</v>
+        <v>2.2629</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2699</v>
+        <v>3.772</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4526</v>
+        <v>2.2667</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1827</v>
+        <v>1.5053</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8672</v>
+        <v>3.8382</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7428</v>
+        <v>2.4175</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1244</v>
+        <v>1.4207</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.0663</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2901</v>
+        <v>-0.1508</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3071</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>1.297</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1117</v>
+        <v>-3.891</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4087</v>
+        <v>2.7793</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1306</v>
+        <v>-0.715</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3793</v>
+        <v>-0.2649</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5099</v>
+        <v>-0.4502</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8883</v>
+        <v>1.5733</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8883</v>
+        <v>1.5733</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.2499</v>
+        <v>3.1288</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8639</v>
+        <v>1.8272</v>
       </c>
       <c r="F19" t="n">
-        <v>2.386</v>
+        <v>1.3016</v>
       </c>
       <c r="G19" t="n">
-        <v>3.772</v>
+        <v>0.2699</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2667</v>
+        <v>0.4526</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5053</v>
+        <v>-0.1827</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8382</v>
+        <v>0.8672</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4175</v>
+        <v>0.7428</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4207</v>
+        <v>0.1244</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0663</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1508</v>
+        <v>-0.2901</v>
       </c>
       <c r="O19" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.3071</v>
       </c>
       <c r="P19" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-1.1117</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-3.891</v>
-      </c>
       <c r="R19" t="n">
-        <v>2.7793</v>
+        <v>2.4087</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9836</v>
+        <v>-0.3264</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6566</v>
+        <v>0.1834</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3271</v>
+        <v>-0.5099</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5733</v>
+        <v>1.8883</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5733</v>
+        <v>1.8883</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.1132</v>
+        <v>2.8103</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5881999999999999</v>
+        <v>2.8103</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5251</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2517</v>
+        <v>2.8103</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2853</v>
+        <v>0.3221</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0337</v>
+        <v>2.4883</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4798</v>
+        <v>2.8103</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4845</v>
+        <v>0.3221</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9953</v>
+        <v>2.4883</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2281</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8008999999999999</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.029</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2883</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3444</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.8103</v>
+        <v>2.6912</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8103</v>
+        <v>2.8028</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0.1115</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8103</v>
+        <v>1.5912</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3221</v>
+        <v>0.4469</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4883</v>
+        <v>1.1444</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8103</v>
+        <v>1.8809</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3221</v>
+        <v>0.4294</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4883</v>
+        <v>1.4515</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-0.2897</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.0174</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.3071</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.1871</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.6753</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.5183</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.1471</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4858</v>
+        <v>2.5406</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4718</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.014</v>
+        <v>2.54</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0764</v>
+        <v>1.2517</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2716</v>
+        <v>1.2853</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8048</v>
+        <v>-0.0337</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1072</v>
+        <v>1.4798</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0859</v>
+        <v>0.4845</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0214</v>
+        <v>0.9953</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9692</v>
+        <v>-0.2281</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1857</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7834</v>
+        <v>-1.029</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.4087</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2236</v>
+        <v>0.7156</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1057</v>
+        <v>0.3563</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1179</v>
+        <v>0.3594</v>
       </c>
       <c r="V22" t="n">
-        <v>0.63</v>
+        <v>0.9439</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2589</v>
+        <v>0.9439</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4707</v>
+        <v>2.1674</v>
       </c>
       <c r="E23" t="n">
-        <v>2.6069</v>
+        <v>1.178</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1361</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5912</v>
+        <v>1.0764</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4469</v>
+        <v>0.2716</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1444</v>
+        <v>0.8048</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8809</v>
+        <v>0.1072</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4294</v>
+        <v>0.0859</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4515</v>
+        <v>0.0214</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2897</v>
+        <v>0.9692</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0174</v>
+        <v>0.1857</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3071</v>
+        <v>0.7834</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0829</v>
+        <v>-0.0948</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.383</v>
+        <v>-0.1881</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6999</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>2.5183</v>
+        <v>0.63</v>
       </c>
       <c r="W23" t="n">
-        <v>3.1471</v>
+        <v>1.2589</v>
       </c>
       <c r="X23" t="n">
         <v>-0.6289</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1451</v>
+        <v>1.7733</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8794</v>
+        <v>-0.4877</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0245</v>
+        <v>2.261</v>
       </c>
       <c r="G24" t="n">
         <v>0.9302</v>
@@ -2326,13 +2326,13 @@
         <v>2.4087</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.341</v>
+        <v>0.2873</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3619</v>
+        <v>0.0299</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0209</v>
+        <v>0.2574</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6209</v>
+        <v>1.5195</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7433</v>
+        <v>-1.2537</v>
       </c>
       <c r="F25" t="n">
-        <v>2.3642</v>
+        <v>2.7731</v>
       </c>
       <c r="G25" t="n">
         <v>1.1403</v>
@@ -2404,13 +2404,13 @@
         <v>3.5205</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4166</v>
+        <v>0.0731</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5295</v>
+        <v>-0.1206</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3144</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3933</v>
+        <v>-0.1734</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5698</v>
+        <v>-1.276</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1765</v>
+        <v>1.1026</v>
       </c>
       <c r="G26" t="n">
         <v>-0.3762</v>
@@ -2482,13 +2482,13 @@
         <v>1.4823</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.4822</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6019</v>
+        <v>-0.3081</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1002</v>
+        <v>-0.1741</v>
       </c>
       <c r="V26" t="n">
         <v>0.3144</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.3891</v>
+        <v>-1.1681</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5027</v>
+        <v>0.6006</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.8917</v>
+        <v>-1.7686</v>
       </c>
       <c r="G27" t="n">
         <v>1.9371</v>
@@ -2560,13 +2560,13 @@
         <v>0.9264</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.1055</v>
+        <v>-0.8845</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6566</v>
+        <v>-0.5586</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4489</v>
+        <v>-0.3258</v>
       </c>
       <c r="V27" t="n">
         <v>-3.1471</v>
@@ -2593,10 +2593,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.8417</v>
+        <v>-2.0375</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.2697</v>
+        <v>-3.4656</v>
       </c>
       <c r="F28" t="n">
         <v>1.428</v>
@@ -2638,10 +2638,10 @@
         <v>1.8529</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.4253</v>
+        <v>-0.6211</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1131</v>
+        <v>-0.309</v>
       </c>
       <c r="U28" t="n">
         <v>-0.3121</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>34.9066</v>
+        <v>36.21249999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>17.7757</v>
+        <v>17.7756</v>
       </c>
       <c r="F29" t="n">
-        <v>17.1312</v>
+        <v>18.4369</v>
       </c>
       <c r="G29" t="n">
         <v>23.1493</v>
@@ -2716,13 +2716,13 @@
         <v>25.9402</v>
       </c>
       <c r="S29" t="n">
-        <v>-3.8551</v>
+        <v>-2.5493</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.6900999999999999</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.165</v>
+        <v>-1.8592</v>
       </c>
       <c r="V29" t="n">
         <v>9.127699999999999</v>
